--- a/RootPath_Revenue_Model.xlsx
+++ b/RootPath_Revenue_Model.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\MicroStep\RootPath\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04e9bb415d956f31/Desktop/solfound/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5090CB7-4311-4E56-8B41-6C3A949E0F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{C5090CB7-4311-4E56-8B41-6C3A949E0F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92BAE0F4-814C-4A7B-ACDC-484349079B3B}"/>
   <bookViews>
-    <workbookView xWindow="-8130" yWindow="-16365" windowWidth="29040" windowHeight="15720" tabRatio="812" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11730" yWindow="-16695" windowWidth="29040" windowHeight="15720" tabRatio="812" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
-    <sheet name="COG" sheetId="8" r:id="rId2"/>
-    <sheet name="Overhead" sheetId="2" r:id="rId3"/>
-    <sheet name="Products" sheetId="3" r:id="rId4"/>
-    <sheet name="Pricing" sheetId="4" r:id="rId5"/>
-    <sheet name="Projections" sheetId="5" r:id="rId6"/>
-    <sheet name="Ramp-Up" sheetId="6" r:id="rId7"/>
-    <sheet name="Guide" sheetId="7" r:id="rId8"/>
+    <sheet name="Overhead" sheetId="2" r:id="rId2"/>
+    <sheet name="Products" sheetId="3" r:id="rId3"/>
+    <sheet name="Pricing" sheetId="4" r:id="rId4"/>
+    <sheet name="Projections" sheetId="5" r:id="rId5"/>
+    <sheet name="Ramp-Up" sheetId="6" r:id="rId6"/>
+    <sheet name="Guide" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="185">
   <si>
     <t>⚙️  UNIVERSAL REVENUE MODEL v3 — INPUTS</t>
   </si>
@@ -616,121 +615,7 @@
     <t>Dill</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Purchases</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Beds</t>
-  </si>
-  <si>
-    <t>Dirt</t>
-  </si>
-  <si>
-    <t>Lattice</t>
-  </si>
-  <si>
-    <t>Fertalizer</t>
-  </si>
-  <si>
-    <t>Sun Covers</t>
-  </si>
-  <si>
-    <t>Frost Covers</t>
-  </si>
-  <si>
-    <t>Seedling Cups</t>
-  </si>
-  <si>
-    <t>Pots</t>
-  </si>
-  <si>
-    <t>Butcher Paper</t>
-  </si>
-  <si>
-    <t>Ribbon</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>watermelon</t>
-  </si>
-  <si>
-    <t>catalope</t>
-  </si>
-  <si>
-    <t>marigold</t>
-  </si>
-  <si>
     <t>Basil Seed Packs</t>
-  </si>
-  <si>
-    <t>flower pot coasters</t>
-  </si>
-  <si>
-    <t>underground terra bulbs</t>
-  </si>
-  <si>
-    <t>saffron</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Seed Type</t>
-  </si>
-  <si>
-    <t>Amazon Receipt - Gmail</t>
-  </si>
-  <si>
-    <t>Seedling Trays (20 spots)</t>
-  </si>
-  <si>
-    <t>Seed Envelopes</t>
-  </si>
-  <si>
-    <t>Plant Type</t>
-  </si>
-  <si>
-    <t>Guava</t>
-  </si>
-  <si>
-    <t>Persimmon</t>
-  </si>
-  <si>
-    <t>Seed Box</t>
-  </si>
-  <si>
-    <t>Smart System</t>
-  </si>
-  <si>
-    <t>Capacity Soil Moisture Kit</t>
-  </si>
-  <si>
-    <t>Raspberry Pi 4 Kit</t>
-  </si>
-  <si>
-    <t>BreadBoard Cables</t>
-  </si>
-  <si>
-    <t>Breadboards</t>
-  </si>
-  <si>
-    <t>Lemon Thyme</t>
-  </si>
-  <si>
-    <t>Mona Lavender</t>
-  </si>
-  <si>
-    <t>Temu Receipt - Gmail</t>
-  </si>
-  <si>
-    <t>Type</t>
   </si>
 </sst>
 </file>
@@ -1244,13 +1129,13 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1791,396 +1676,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2000F6C7-FBAA-4E63-9E58-32DFA389D4C6}">
-  <sheetPr>
-    <tabColor rgb="FF7030A0"/>
-  </sheetPr>
-  <dimension ref="A1:K46"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" customWidth="1"/>
-    <col min="6" max="6" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="C1" s="73" t="s">
-        <v>186</v>
-      </c>
-      <c r="D1" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="E1" s="73" t="s">
-        <v>222</v>
-      </c>
-      <c r="F1" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="K1" s="73"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="71"/>
-      <c r="B2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C2" s="72"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="71"/>
-      <c r="B3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="71"/>
-      <c r="B4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C4" s="72"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="71"/>
-      <c r="B5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C5" s="72"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="71"/>
-      <c r="B6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" s="72"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="71"/>
-      <c r="B7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="72"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="71"/>
-      <c r="B8" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="72"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="71"/>
-      <c r="B9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="72"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10" s="71">
-        <v>45698</v>
-      </c>
-      <c r="B10" t="s">
-        <v>208</v>
-      </c>
-      <c r="C10" s="72">
-        <f>38.96</f>
-        <v>38.96</v>
-      </c>
-      <c r="D10">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11" s="71">
-        <v>45698</v>
-      </c>
-      <c r="B11" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="72">
-        <f>15.78</f>
-        <v>15.78</v>
-      </c>
-      <c r="D11">
-        <v>120</v>
-      </c>
-      <c r="F11" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="71"/>
-      <c r="B12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="72"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="71"/>
-      <c r="B13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C13" s="72"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="71"/>
-      <c r="B14" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="71"/>
-      <c r="B15" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="71"/>
-      <c r="B16" t="s">
-        <v>196</v>
-      </c>
-      <c r="C16" s="72">
-        <f>9.99*1.0825</f>
-        <v>10.814175000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="71"/>
-      <c r="C17" s="72"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="71">
-        <v>46047</v>
-      </c>
-      <c r="B18" t="s">
-        <v>202</v>
-      </c>
-      <c r="C18" s="72">
-        <f>7.88*1.082</f>
-        <v>8.5261600000000008</v>
-      </c>
-      <c r="F18" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="71">
-        <v>46047</v>
-      </c>
-      <c r="B19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C19" s="72">
-        <f>41.64*1.082</f>
-        <v>45.054480000000005</v>
-      </c>
-      <c r="F19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="B23" s="73" t="s">
-        <v>206</v>
-      </c>
-      <c r="C23" s="73" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="E23" s="73"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B26" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B27" t="s">
-        <v>204</v>
-      </c>
-      <c r="C27">
-        <f>7.69*1.0825</f>
-        <v>8.3244249999999997</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="F27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="B32" s="73" t="s">
-        <v>210</v>
-      </c>
-      <c r="C32" s="73" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="E32" s="73"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B33" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B34" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B35" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B38" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="B42" s="73" t="s">
-        <v>214</v>
-      </c>
-      <c r="C42" s="73" t="s">
-        <v>205</v>
-      </c>
-      <c r="D42" s="73" t="s">
-        <v>186</v>
-      </c>
-      <c r="E42" s="73"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="71">
-        <v>45788</v>
-      </c>
-      <c r="B43" t="s">
-        <v>215</v>
-      </c>
-      <c r="C43">
-        <v>4</v>
-      </c>
-      <c r="D43">
-        <f>18.99*1.0825</f>
-        <v>20.556674999999998</v>
-      </c>
-      <c r="F43" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="71">
-        <v>45788</v>
-      </c>
-      <c r="B44" t="s">
-        <v>216</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <f>112.49*1.0825</f>
-        <v>121.770425</v>
-      </c>
-      <c r="F44" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="71"/>
-      <c r="B45" t="s">
-        <v>217</v>
-      </c>
-      <c r="C45">
-        <v>120</v>
-      </c>
-      <c r="D45">
-        <f>6.98*1.0825</f>
-        <v>7.5558500000000004</v>
-      </c>
-      <c r="F45" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="71"/>
-      <c r="B46" t="s">
-        <v>218</v>
-      </c>
-      <c r="C46">
-        <v>2</v>
-      </c>
-      <c r="F46" t="s">
-        <v>207</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{344DCE31-5AD8-4913-B7AD-7B1FB3D8CE2B}">
-          <x14:formula1>
-            <xm:f>Overhead!$A$5:$A$10+Overhead!$A$13:$A$16</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E53</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1A3A5C"/>
@@ -2568,7 +2063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E7D52"/>
@@ -3030,7 +2525,7 @@
     </row>
     <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="B23" s="33" t="s">
         <v>81</v>
@@ -3326,7 +2821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1A4A6B"/>
@@ -5870,7 +5365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FFB8860B"/>
@@ -7348,7 +6843,7 @@
       </c>
       <c r="B52" s="78"/>
       <c r="C52" s="79"/>
-      <c r="D52" s="87">
+      <c r="D52" s="88">
         <f>SUMIF(A4:A50,"&lt;&gt;",D4:D50)</f>
         <v>2942.5365565819875</v>
       </c>
@@ -7362,7 +6857,7 @@
       </c>
       <c r="B53" s="78"/>
       <c r="C53" s="79"/>
-      <c r="D53" s="87">
+      <c r="D53" s="88">
         <f>SUMIF(A4:A50,"&lt;&gt;",E4:E50)</f>
         <v>1211.632699769053</v>
       </c>
@@ -7376,7 +6871,7 @@
       </c>
       <c r="B54" s="78"/>
       <c r="C54" s="79"/>
-      <c r="D54" s="87">
+      <c r="D54" s="88">
         <f>SUMIF(A4:A50,"&lt;&gt;",E4:E50)*4.33</f>
         <v>5246.3695899999993</v>
       </c>
@@ -7385,7 +6880,7 @@
       <c r="G54" s="79"/>
     </row>
     <row r="55" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="89"/>
+      <c r="A55" s="87"/>
       <c r="B55" s="75"/>
       <c r="C55" s="75"/>
       <c r="D55" s="75"/>
@@ -7399,7 +6894,7 @@
       </c>
       <c r="B56" s="78"/>
       <c r="C56" s="79"/>
-      <c r="D56" s="88">
+      <c r="D56" s="89">
         <f>Inputs!B11</f>
         <v>800</v>
       </c>
@@ -7413,7 +6908,7 @@
       </c>
       <c r="B57" s="78"/>
       <c r="C57" s="79"/>
-      <c r="D57" s="88">
+      <c r="D57" s="89">
         <f>SUMIF(A4:A50,"&lt;&gt;",E4:E50)-Inputs!B11</f>
         <v>411.63269976905303</v>
       </c>
@@ -7422,7 +6917,7 @@
       <c r="G57" s="79"/>
     </row>
     <row r="58" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="89"/>
+      <c r="A58" s="87"/>
       <c r="B58" s="75"/>
       <c r="C58" s="75"/>
       <c r="D58" s="75"/>
@@ -7459,7 +6954,7 @@
       <c r="G60" s="79"/>
     </row>
     <row r="61" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="89"/>
+      <c r="A61" s="87"/>
       <c r="B61" s="75"/>
       <c r="C61" s="75"/>
       <c r="D61" s="75"/>
@@ -7487,7 +6982,7 @@
       </c>
       <c r="B63" s="78"/>
       <c r="C63" s="79"/>
-      <c r="D63" s="87">
+      <c r="D63" s="88">
         <f>SUMIF(A4:A50,"&lt;&gt;",E4:E50)*4.33*(1-Inputs!B16)</f>
         <v>4459.4141514999992</v>
       </c>
@@ -7497,6 +6992,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="D56:G56"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="A58:G58"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A61:G61"/>
     <mergeCell ref="A1:G1"/>
@@ -7513,13 +7015,6 @@
     <mergeCell ref="D59:G59"/>
     <mergeCell ref="D60:G60"/>
     <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="D63:G63"/>
-    <mergeCell ref="D56:G56"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="A58:G58"/>
   </mergeCells>
   <conditionalFormatting sqref="D57:G57">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -7533,7 +7028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC0392B"/>
@@ -7809,7 +7304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF555555"/>
